--- a/Directorio de datos.xlsx
+++ b/Directorio de datos.xlsx
@@ -5,11 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabla datos_crudos" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Tabla datos_limpios" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Tabla staging_datos_crudos" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Tabla staging_datos_limpios" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Tabla Prestadores(Madre)" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Tabla SedePrestadores(Hija)" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="vista_caracterizacion_juridica " sheetId="5" state="visible" r:id="rId7"/>
